--- a/Partner Resources/ICD10 to CCB Causes/ICD10-to-CCB-Cause.xlsx
+++ b/Partner Resources/ICD10 to CCB Causes/ICD10-to-CCB-Cause.xlsx
@@ -14,9 +14,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="773">
-  <si>
-    <t xml:space="preserve">Last Updated: March 28, 2025</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="778">
+  <si>
+    <t xml:space="preserve">Last Updated: December 18, 2025</t>
   </si>
   <si>
     <t xml:space="preserve">First sheet: Public Health Level Link</t>
@@ -76,7 +76,7 @@
     <t xml:space="preserve">A1[5-9]|B90</t>
   </si>
   <si>
-    <t xml:space="preserve">Communicable</t>
+    <t xml:space="preserve">Communicable, maternal, and nutritional conditions</t>
   </si>
   <si>
     <t xml:space="preserve">A02</t>
@@ -237,7 +237,7 @@
     <t xml:space="preserve">D370|C0[0-8]|D103|D11[0,7,9]|C11|D106|C09|C1[0,2-4]</t>
   </si>
   <si>
-    <t xml:space="preserve">Cancer</t>
+    <t xml:space="preserve">Cancer/Neoplasms</t>
   </si>
   <si>
     <t xml:space="preserve">B02</t>
@@ -469,7 +469,7 @@
     <t xml:space="preserve">I1[0-5]|I272</t>
   </si>
   <si>
-    <t xml:space="preserve">Cardiovascular</t>
+    <t xml:space="preserve">Cardiovascular diseases</t>
   </si>
   <si>
     <t xml:space="preserve">C02</t>
@@ -568,7 +568,7 @@
     <t xml:space="preserve">Other or unspecified cardiovascular diseases</t>
   </si>
   <si>
-    <t xml:space="preserve">I01-I09, I00, I270, I273-I280, I44-149 (minus I469, I48, I471, I495) ,I51 (minus I513), I700-I849 (minus I74, I822, I23, I828, I829), I851-I858, I86-I99</t>
+    <t xml:space="preserve">I01-I09, I00, I270, I273-I280, I44-149 (minus I469, I48, I471, I495) ,I51 (minus I513), I700-I849 (minus I74, I822, I823, I828, I829), I851-I858, I86-I99</t>
   </si>
   <si>
     <t xml:space="preserve">I0[1-9]|I00|I27[0,3-9]|I28|I4[4-5]|I46[0-8]|I47[0, 2-9]|I49[0-4, 6-9]|I51[0-2, 4-9]|I7[0-3, 5-9]|I8[0-1, 3-4, 6-9]|I82[0-1, 4-7]|I85[1-8]|I9</t>
@@ -625,7 +625,7 @@
     <t xml:space="preserve">D06</t>
   </si>
   <si>
-    <t xml:space="preserve">Alzheimer’s disease and other dementias</t>
+    <t xml:space="preserve">Alzheimer's disease and other dementias</t>
   </si>
   <si>
     <t xml:space="preserve">F00, G30, F02-F03, G311, G318-G319, F01, G310</t>
@@ -694,277 +694,334 @@
     <t xml:space="preserve">K70[5-8]|K71[3-5,7]|K72[1-9]|K7[3-6]|I85[0,9]</t>
   </si>
   <si>
-    <t xml:space="preserve">D12</t>
+    <t xml:space="preserve">D13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Urinary tract infection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N340-342, N390</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N34[0-2]|N390</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obesity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hypothyroidism</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E031, E034-035, E038-039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E03[1, 4-5, 8-9]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hyperlipidemia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E780-785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E78[0-5]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chronic obstructive pulmonary disease</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J40-J44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J4[0-4]|J98[2-3]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asthma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J45-J46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J4[5-6]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other respiratory diseases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J30-J39, J47-J98 (minus J690, J80, J841, J849, J960, J961, J969, J982-983)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J[3, 5, 7]|J6[0-8]|J69[1-9]|J8[1-3, 5-9]|J84[0, 2-8]|J4[7-9]|J9[0-5, 7]|J96[2-8]|J98[0-1, 4-9]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Respiratory failure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J960, J961, J969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J96[0-1, 9]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interstitial lung disease</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J841, J849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J84[1, 9]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aspiration pneumonitis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J690</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARDS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other Chronic Conditions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H40, H25-H26, H49-H52, H35.3, H30-H35 (minus H35.3), H53-H54, H90-H91, H00-H21, H27, H43-H47, H55-H61, H69-H83, H92-H93, N40, N20-N23, N25-N39 (minus N340-342,  N390), N41-N45, N47-N51, N46, N97, N60-N64, N75-N76, N80-N96, N98, L00-L98, M05-M06, M15-M19, M10, M45-M48, M50-M54, I271, M00, M02, M08, M11-M13, M20-M43, M60-M724, M727-M99, K02, K05, —, K00, K01, K03, K04, K06-K14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H40|H2[5-6]|H49|H5[0-2]|H353|H3[0-4]|\\bH35\\b|H35[0-2,4-9]|H5[3-4]|H9[0-1]|H0|H1|H2[0-1,7]|H4[3-7]|H5[5-9]|H6[0-1,9]|H7|H8[0-3]|H9[2-3]|N40|N2[0-3]|N2[5-9]|N3[0-3, 5-8]|N34[3-9]|N39[1-9]|N4[1-5,7-9]|N5[0-1]|N46|N97|N6[0-4]|N7[5-6]|N8|N9[0-6,8]|L[0-8]|L9[0-8]|M0[5-6]|M1[5-9]|M10|M4[5-8]|M5[0-4]|I271|M0[0,2,8]|M1[1-3]|M[2-3,6,8-9]|M4[0-3]|M7[0-1,3-9]|M72[0-4,7-9]|K02|K05|-|K0[0-1,3-4,6-9]|K1[0-4]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Road injury</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V01-V99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Injuries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drug overdose (poisoning/substance use disorders)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X40- X44, F11, F14, F12, F15, F13, F16, F18, F19, P044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X4[0-4]|F11|F14|F12|F15|F1[3,6,8,9]|P044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alcohol-related conditions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K700-K704, K709, F10, G721, P043, Q860, X45, Y15, Y91, G621, G312, I426, K292, K852, K860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K70[0-4, 9]|F10|G721|P043|Q860|X45|Y15|Y91|G621|G312|I426|K292|K852|K860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poisonings (non-drug)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X46-X49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X4[6-9]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Falls</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W00-W19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W[0-1]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other unintentional injuries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X00-X19, W65-W74, W20-W38, W40-W43, W45, W46, W49-W52, W76, W32-W34.9, X33-X38, S, W39, W44, W53-W64, W75, W77-W99, X20-X32, X39, X50-X59, Y40-Y86, Y88, Y892-Y899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X[0-1]|W6[5-9]|W7[0-4]|W2|W3[0-1,5-8]|W4[0-3,5-6,9]|W5[0-2]|W7[6]|W3[2-4]|X3[3-8]|S|W39|W44|W5[3-9]|W6[0-4]|W7[5, 7-9]|W[8-9]|X[2,5]|X3[0-2,9]|Y[4-7]|Y8[0-6,8]|Y89[2-9]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suicide/Self-harm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U031, U039, X60-X84, Y870</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U03[1,9]|X[6-7]|X8[0-4]|Y870</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homicide/Interpersonal violence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U010-U019, U02, X85-Y09, Y871, Y350-354, Y356-Y357, Y358-Y359,Y890, Y355,  Y36, Y891, Y38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U01[0-9]|U02|X8[5-9]|X9|Y0|Y871|Y35[0-4]|Y35[6-9]|Y890|Y355|Y36|Y37|Y891|Y38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Injuries of unknown intent (e.g., unintentional or self-harm), including overdoses and deaths by firearm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U070, Y10-14, Y16-34, Y872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U070|Y1[0-4,6-9]|Y2|Y3[0-4]|Y872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Short gestation, low birth weight, slow growth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P05, P07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P05|P07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perinatal conditions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perinatal respiratory distress/conditions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P20-P28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P2[0-8]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perinatal cardiovascular disorders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infections and other disorders of newborn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P35-P39 (excluding P37.3, P37.4), P50-61, P77</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P3[5-6,8-9]|P37[0-2,5-9]|P5|P6[0-1]|P77</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sudden unexplained death syndrome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R95, R99 (only in &lt;1 year old), W75 (only in &lt;1 year old)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Newborn affected by complications of pregnancy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P00-P03, P041-P042, P045-49, P08, P09, P10-P15, P19, P50-P96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P0[0-3,8,9]|P04[1-2,5-9]|P1[0-5]|P19|P7[0-6,8-9]|P8|P9[0-6]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P07</t>
   </si>
   <si>
     <t xml:space="preserve">Congenital anomalies</t>
   </si>
   <si>
-    <t xml:space="preserve">Q00, Q05, Q35-Q37, Q90, Q20-Q28, Q91-Q99, Q01-Q04, Q06-Q18, Q30-Q34, Q38-Q89</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q0[0,5]|Q3[5-7]|Q90|Q2[0-8]|Q9[1-9]|Q0[1-4,6-9]|Q1[0-8]|Q3[0-4,8-9]|Q[4-7]|Q8[0-5,7-9]|Q86[1-9]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Urinary tract infection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N340-342, N390</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N34[0-2]|N390</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Obesity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E66</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hypothyroidism</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E031, E034-035, E038-039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E03[1, 4-5, 8-9]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hyperlipidemia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E780-785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E78[0-5]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D66</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chronic obstructive pulmonary disease</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J40-J44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J4[0-4]|J98[2-3]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asthma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J45-J46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J4[5-6]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D68</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other respiratory diseases</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J30-J39, J47-J98 (minus J690, J80, J841, J849, J960, J961, J969, J982-983)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J[3, 5, 7]|J6[0-8]|J69[1-9]|J8[1-3, 5-9]|J84[0, 2-8]|J4[7-9]|J9[0-5, 7]|J96[2-8]|J98[0-1, 4-9]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D69</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Respiratory failure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J960, J961, J969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J96[0-1, 9]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interstitial lung disease</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J841, J849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J84[1, 9]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D71</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aspiration pneumonitis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J690</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARDS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other Chronic Conditions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H40, H25-H26, H49-H52, H35.3, H30-H35 (minus H35.3), H53-H54, H90-H91, H00-H21, H27, H43-H47, H55-H61, H69-H83, H92-H93, N40, N20-N23, N25-N39 (minus N340-342,  N390), N41-N45, N47-N51, N46, N97, N60-N64, N75-N76, N80-N96, N98, L00-L98, M05-M06, M15-M19, M10, M45-M48, M50-M54, I271, M00, M02, M08, M11-M13, M20-M43, M60-M724, M727-M99, K02, K05, —, K00, K01, K03, K04, K06-K14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H40|H2[5-6]|H49|H5[0-2]|H353|H3[0-4]|\\bH35\\b|H35[0-2,4-9]|H5[3-4]|H9[0-1]|H0|H1|H2[0-1,7]|H4[3-7]|H5[5-9]|H6[0-1,9]|H7|H8[0-3]|H9[2-3]|N40|N2[0-3]|N2[5-9]|N3[0-3, 5-8]|N34[3-9]|N39[1-9]|N4[1-5,7-9]|N5[0-1]|N46|N97|N6[0-4]|N7[5-6]|N8|N9[0-6,8]|L[0-8]|L9[0-8]|M0[5-6]|M1[5-9]|M10|M4[5-8]|M5[0-4]|I271|M0[0,2,8]|M1[1-3]|M[2-3,6,8-9]|M4[0-3]|M7[0-1,3-9]|M72[0-4,7-9]|K02|K05|-|K0[0-1,3-4,6-9]|K1[0-4]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Road injury</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V01-V99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Injury</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drug overdose (poisoning/substance use disorders)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X40- X44, F11, F14, F12, F15, F13, F16, F18, F19, P044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X4[0-4]|F11|F14|F12|F15|F1[3,6,8,9]|P044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alcohol-related conditions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K700-K704, K709, F10, G721, P043, Q860, X45, Y15, Y91, G621, G312, I426, K292, K852, K860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K70[0-4, 9]|F10|G721|P043|Q860|X45|Y15|Y91|G621|G312|I426|K292|K852|K860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Poisonings (non-drug)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X46-X49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X4[6-9]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Falls</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W00-W19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W[0-1]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other unintentional injuries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X00-X19, W65-W74, W20-W38, W40-W43, W45, W46, W49-W52, W75, W76, W32-W34.9, X33-X38, S, W39, W44, W53-W64, W77-W99, X20-X32, X39, X50-X59, Y40-Y86, Y88, Y892-Y899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X[0-1]|W6[5-9]|W7[0-4]|W2|W3[0-1,5-8]|W4[0-3,5-6,9]|W5[0-2]|W7[5-6]|W3[2-4]|X3[3-8]|S|W39|W44|W5[3-9]|W6[0-4]|W7[7-9]|W[8-9]|X[2,5]|X3[0-2,9]|Y[4-7]|Y8[0-6,8]|Y89[2-9]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suicide/Self-harm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U031, U039, X60-X84, Y870</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U03[1,9]|X[6-7]|X8[0-4]|Y870</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Homicide/Interpersonal violence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U010-U019, U02, X85-Y09, Y871, Y350-354, Y356-Y357, Y358-Y359,Y890, Y355,  Y36, Y891, Y38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U01[0-9]|U02|X8[5-9]|X9|Y0|Y871|Y35[0-4]|Y35[6-9]|Y890|Y355|Y36|Y37|Y891|Y38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Injuries of unknown intent (e.g., unintentional or self-harm), including overdoses and deaths by firearm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U070, Y10-14, Y16-34, Y872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U070|Y1[0-4,6-9]|Y2|Y3[0-4]|Y872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neonatal conditions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P05, P07, P22, P27-P28, P23, P03, P10-P15, P20-P21, P24-P26, P29, P35-P39 (excluding P37.3, P37.4), P00-P02, P041-P042, P045-49, P08, P50-P96, P09, P19, R95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P0[5,7]|P2[2,7-8]|P23|P03|P1[0-5]|P2[0-1,4-6,9]|P3[5-6,8-9]|P37[0-2,5-9]|P0[0-2,8,9]|P04[1-2,5-9]|P[5-8]|P9[0-6]|P19|R95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perinatal</t>
+    <t xml:space="preserve">Q00, Q05, Q35-Q37, Q90, Q20-Q29, Q91-Q99, Q01-Q04, Q06-Q19, Q30-Q34, Q38-Q89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q0[0,5]|Q3[5-7]|Q90|Q2[0-9]|Q9[1-9]|Q0[1-4,6-9]|Q1[0-9]|Q3[0-4,8-9]|Q[4-7]|Q8[0-5,7-9]|Q86[1-9]</t>
   </si>
   <si>
     <t xml:space="preserve">Z01</t>
@@ -979,13 +1036,19 @@
     <t xml:space="preserve">R[0-6]|R7[1-2,4-9]|R73[1-8]|R8|R9[0-4,6-9]</t>
   </si>
   <si>
-    <t xml:space="preserve">Ill-Defined</t>
+    <t xml:space="preserve">Unknown/Missing Value</t>
   </si>
   <si>
     <t xml:space="preserve">cause_code_detail</t>
   </si>
   <si>
+    <t xml:space="preserve">cause_code_public_health</t>
+  </si>
+  <si>
     <t xml:space="preserve">cause_name_detail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cause_name_public_health</t>
   </si>
   <si>
     <t xml:space="preserve">A02a</t>
@@ -1564,7 +1627,7 @@
     <t xml:space="preserve">I0[1-9]</t>
   </si>
   <si>
-    <t xml:space="preserve">I00, I270, I273-I280, I44-149 (minus I469, I48, I471, I495) ,I51 (minus I513), I700-I849 (minus I74, I822, I23, I828, I829), I851-I858, I86-I99</t>
+    <t xml:space="preserve">I00, I270, I273-I280, I44-149 (minus I469, I48, I471, I495) ,I51 (minus I513), I700-I849 (minus I74, I822, I823, I828, I829), I851-I858, I86-I99</t>
   </si>
   <si>
     <t xml:space="preserve">I00|I27[0,3-9]|I28|I4[4-5]|I46[0-8]|I47[0, 2-9]|I49[0-4, 6-9]|I51[0-2, 4-9]|I7[0-3, 5-9]|I8[0-1, 3-4, 6-9]|I82[0-1, 4-7]|I85[1-8]|I9</t>
@@ -1720,7 +1783,7 @@
     <t xml:space="preserve">D06a</t>
   </si>
   <si>
-    <t xml:space="preserve">Alzheimer’s  disease</t>
+    <t xml:space="preserve">Alzheimer's  disease</t>
   </si>
   <si>
     <t xml:space="preserve">F00, G30</t>
@@ -1897,6 +1960,351 @@
     <t xml:space="preserve">N0[2-9]|N1</t>
   </si>
   <si>
+    <t xml:space="preserve">Glaucoma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cataracts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H25-H26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H2[5-6]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refractive errors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H49-H52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H49|H5[0-2]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Macular degeneration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H35.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other vision loss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H30-H35 (minus H35.3), H53-H54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H3[0-4]|\\bH35\\b|H35[0-2,4-9]|H5[3-4]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other hearing loss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H90-H91</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H9[0-1]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other sense organ disorders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H00-H21, H27, H43-H47, H55-H61, H69-H83, H92-H93</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H0|H1|H2[0-1,7]|H4[3-7]|H5[5-9]|H6[0-1,9]|H7|H8[0-3]|H9[2-3]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Benign prostatic hyperplasia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Urolithiasis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N20-N23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N2[0-3]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other genitourinary disorders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N25-N39 (minus N340-342,  N390), N41-N45, N47-N51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N2[5-9]|N3[0-3, 5-8]|N34[3-9]|N39[1-9]|N4[1-5,7-9]|N5[0-1]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infertility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N46, N97</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N46|N97</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gynecological diseases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N60-N64, N75-N76, N80-N96, N98</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N6[0-4]|N7[5-6]|N8|N9[0-6,8]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skin diseases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L00-L98</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L[0-8]|L9[0-8]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rheumatoid arthritis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M05-M06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M0[5-6]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Osteoarthritis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M15-M19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M1[5-9]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Back and neck pain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M45-M48, M50-M54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M4[5-8]|M5[0-4]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other musculoskeletal disorders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I271, M00, M02, M08, M11-M13, M20-M43, M60-M724, M727-M99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I271|M0[0,2,8]|M1[1-3]|M[2-3,6,8-9]|M4[0-3]|M7[0-1,3-9]|M72[0-4,7-9]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dental caries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Periodontal disease</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edentulism</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other oral disorders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K00, K01, K03, K04, K06-K14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K0[0-1,3-4,6-9]|K1[0-4]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X40- X44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X4[0-4]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opioid use disorders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cocaine use disorders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cannabis use disorders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other stimulant use disorders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other drug use disorders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F13, F16, F18, F19, P044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F1[3,6,8,9]|P044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E03a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alcoholic liver disease</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K700-K704, K709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K70[0-4, 9]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E03b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other alcohol-related</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F10, G721, P043, Q860, X45, Y15, Y91, G621, G312, I426, K292, K852, K860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F10|G721|P043|Q860|X45|Y15|Y91|G621|G312|I426|K292|K852|K860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fire, heat and hot substances</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X00-X19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X[0-1]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drownings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W65-W74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W6[5-9]|W7[0-4]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exposure to mechanical forces</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W20-W38, W40-W43, W45, W46, W49-W52, W76</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W2|W3[0-1,5-8]|W4[0-3,5-6,9]|W5[0-2]|W7[6]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accidental Firearm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W32-W34.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W3[2-4]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Natural disasters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X33-X38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X3[3-8]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S, W39, W44, W53-W64, W75, W77-W99, X20-X32, X39, X50-X59, Y40-Y86, Y88, Y892-Y899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S|W39|W44|W5[3-9]|W6[0-4]|W7[5, 7-9]|W[8-9]|X[2,5]|X3[0-2,9]|Y[4-7]|Y8[0-6,8]|Y89[2-9]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E08a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homicide excluding legal intervention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U010-U019, U02, X85-Y09, Y871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U01[0-9]|U02|X8[5-9]|X9|Y0|Y871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E08b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legal intervention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y350-354, Y356-Y357, Y358-Y359,Y890</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y35[0-4]|Y35[6-9]|Y890</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E08c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Execution, War, Terrorism</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y355,  Y36, Y891, Y38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y355|Y36|Y37|Y891|Y38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vaping-related disorder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U070</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y10-14, Y16-34, Y872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y1[0-4,6-9]|Y2|Y3[0-4]|Y872</t>
+  </si>
+  <si>
     <t xml:space="preserve">Neural tube defects</t>
   </si>
   <si>
@@ -1924,10 +2332,10 @@
     <t xml:space="preserve">Congenital heart anomalies</t>
   </si>
   <si>
-    <t xml:space="preserve">Q20-Q28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q2[0-8]</t>
+    <t xml:space="preserve">Q20-Q29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q2[0-9]</t>
   </si>
   <si>
     <t xml:space="preserve">Other chromosomal anomalies</t>
@@ -1942,403 +2350,10 @@
     <t xml:space="preserve">Other congenital anomalies</t>
   </si>
   <si>
-    <t xml:space="preserve">Q01-Q04, Q06-Q18, Q30-Q34, Q38-Q89</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q0[1-4,6-9]|Q1[0-8]|Q3[0-4,8-9]|Q[4-7]|Q8[0-5,7-9]|Q86[1-9]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glaucoma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cataracts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H25-H26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H2[5-6]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Refractive errors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H49-H52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H49|H5[0-2]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Macular degeneration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H35.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other vision loss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H30-H35 (minus H35.3), H53-H54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H3[0-4]|\\bH35\\b|H35[0-2,4-9]|H5[3-4]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other hearing loss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H90-H91</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H9[0-1]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other sense organ disorders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H00-H21, H27, H43-H47, H55-H61, H69-H83, H92-H93</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H0|H1|H2[0-1,7]|H4[3-7]|H5[5-9]|H6[0-1,9]|H7|H8[0-3]|H9[2-3]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Benign prostatic hyperplasia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Urolithiasis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N20-N23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N2[0-3]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other genitourinary disorders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N25-N39 (minus N340-342,  N390), N41-N45, N47-N51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N2[5-9]|N3[0-3, 5-8]|N34[3-9]|N39[1-9]|N4[1-5,7-9]|N5[0-1]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infertility</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N46, N97</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N46|N97</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gynecological diseases</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N60-N64, N75-N76, N80-N96, N98</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N6[0-4]|N7[5-6]|N8|N9[0-6,8]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skin diseases</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L00-L98</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L[0-8]|L9[0-8]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rheumatoid arthritis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M05-M06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M0[5-6]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Osteoarthritis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M15-M19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M1[5-9]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Back and neck pain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M45-M48, M50-M54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M4[5-8]|M5[0-4]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other musculoskeletal disorders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I271, M00, M02, M08, M11-M13, M20-M43, M60-M724, M727-M99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I271|M0[0,2,8]|M1[1-3]|M[2-3,6,8-9]|M4[0-3]|M7[0-1,3-9]|M72[0-4,7-9]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dental caries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Periodontal disease</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edentulism</t>
-  </si>
-  <si>
-    <t xml:space="preserve">—</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other oral disorders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K00, K01, K03, K04, K06-K14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K0[0-1,3-4,6-9]|K1[0-4]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X40- X44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X4[0-4]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Opioid use disorders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cocaine use disorders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cannabis use disorders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other stimulant use disorders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other drug use disorders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F13, F16, F18, F19, P044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F1[3,6,8,9]|P044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E03a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alcoholic liver disease</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K700-K704, K709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K70[0-4, 9]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E03b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other alcohol-related</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F10, G721, P043, Q860, X45, Y15, Y91, G621, G312, I426, K292, K852, K860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F10|G721|P043|Q860|X45|Y15|Y91|G621|G312|I426|K292|K852|K860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fire, heat and hot substances</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X00-X19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X[0-1]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drownings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W65-W74</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W6[5-9]|W7[0-4]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exposure to mechanical forces</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W20-W38, W40-W43, W45, W46, W49-W52, W75, W76</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W2|W3[0-1,5-8]|W4[0-3,5-6,9]|W5[0-2]|W7[5-6]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accidental Firearm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W32-W34.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W3[2-4]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Natural disasters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X33-X38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X3[3-8]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S, W39, W44, W53-W64, W77-W99, X20-X32, X39, X50-X59, Y40-Y86, Y88, Y892-Y899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S|W39|W44|W5[3-9]|W6[0-4]|W7[7-9]|W[8-9]|X[2,5]|X3[0-2,9]|Y[4-7]|Y8[0-6,8]|Y89[2-9]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E08a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Homicide excluding legal intervention</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U010-U019, U02, X85-Y09, Y871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U01[0-9]|U02|X8[5-9]|X9|Y0|Y871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E08b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legal intervention</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Y350-354, Y356-Y357, Y358-Y359,Y890</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Y35[0-4]|Y35[6-9]|Y890</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E08c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Execution, War, Terrorism</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Y355,  Y36, Y891, Y38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Y355|Y36|Y37|Y891|Y38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vaping-related disorder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U070</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Y10-14, Y16-34, Y872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Y1[0-4,6-9]|Y2|Y3[0-4]|Y872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preterm birth complications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P05, P07, P22, P27-P28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P0[5,7]|P2[2,7-8]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Congenital pneumonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Birth asphyxia and birth trauma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P03, P10-P15, P20-P21, P24-P26, P29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P03|P1[0-5]|P2[0-1,4-6,9]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neonatal sepsis and infections</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P35-P39 (excluding P37.3, P37.4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P3[5-6,8-9]|P37[0-2,5-9]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other neonatal conditions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P00-P02, P041-P042, P045-49, P08, P50-P96, P09, P19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P0[0-2,8,9]|P04[1-2,5-9]|P[5-8]|P9[0-6]|P19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sudden infant death syndrome</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R95</t>
+    <t xml:space="preserve">Q01-Q04, Q06-Q19, Q30-Q34, Q38-Q89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q0[1-4,6-9]|Q1[0-9]|Q3[0-4,8-9]|Q[4-7]|Q8[0-5,7-9]|Q86[1-9]</t>
   </si>
 </sst>
 </file>
@@ -2427,8 +2442,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:E77" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:E77"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:E82" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:E82"/>
   <tableColumns count="5">
     <tableColumn id="1" name="cause_code"/>
     <tableColumn id="2" name="cause_name"/>
@@ -2445,9 +2460,9 @@
   <autoFilter ref="A1:G208"/>
   <tableColumns count="7">
     <tableColumn id="1" name="cause_code_detail"/>
-    <tableColumn id="2" name="cause_code"/>
+    <tableColumn id="2" name="cause_code_public_health"/>
     <tableColumn id="3" name="cause_name_detail"/>
-    <tableColumn id="4" name="cause_name"/>
+    <tableColumn id="4" name="cause_name_public_health"/>
     <tableColumn id="5" name="broad_condition_group"/>
     <tableColumn id="6" name="icd10_code"/>
     <tableColumn id="7" name="icd10_regex"/>
@@ -3764,7 +3779,7 @@
         <v>231</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E55" t="s">
         <v>189</v>
@@ -3772,13 +3787,13 @@
     </row>
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="s">
+        <v>232</v>
+      </c>
+      <c r="B56" t="s">
         <v>233</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C56" s="4" t="s">
         <v>234</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>235</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>235</v>
@@ -3900,7 +3915,7 @@
         <v>262</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E63" t="s">
         <v>189</v>
@@ -3908,16 +3923,16 @@
     </row>
     <row r="64" ht="40" customHeight="1">
       <c r="A64" t="s">
+        <v>263</v>
+      </c>
+      <c r="B64" t="s">
         <v>264</v>
       </c>
-      <c r="B64" t="s">
+      <c r="C64" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="C64" s="4" t="s">
-        <v>266</v>
-      </c>
       <c r="D64" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E64" t="s">
         <v>189</v>
@@ -3925,13 +3940,13 @@
     </row>
     <row r="65" ht="40" customHeight="1">
       <c r="A65" t="s">
+        <v>266</v>
+      </c>
+      <c r="B65" t="s">
         <v>267</v>
       </c>
-      <c r="B65" t="s">
+      <c r="C65" s="4" t="s">
         <v>268</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>269</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>269</v>
@@ -3954,24 +3969,24 @@
         <v>273</v>
       </c>
       <c r="E66" t="s">
-        <v>189</v>
+        <v>274</v>
       </c>
     </row>
     <row r="67" ht="40" customHeight="1">
       <c r="A67" t="s">
+        <v>275</v>
+      </c>
+      <c r="B67" t="s">
+        <v>276</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="E67" t="s">
         <v>274</v>
-      </c>
-      <c r="B67" t="s">
-        <v>275</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="E67" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="68" ht="40" customHeight="1">
@@ -3988,7 +4003,7 @@
         <v>282</v>
       </c>
       <c r="E68" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="69" ht="40" customHeight="1">
@@ -4005,7 +4020,7 @@
         <v>286</v>
       </c>
       <c r="E69" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="70" ht="40" customHeight="1">
@@ -4022,7 +4037,7 @@
         <v>290</v>
       </c>
       <c r="E70" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="71" ht="40" customHeight="1">
@@ -4039,7 +4054,7 @@
         <v>294</v>
       </c>
       <c r="E71" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="72" ht="40" customHeight="1">
@@ -4056,7 +4071,7 @@
         <v>298</v>
       </c>
       <c r="E72" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="73" ht="40" customHeight="1">
@@ -4073,7 +4088,7 @@
         <v>302</v>
       </c>
       <c r="E73" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="74" ht="40" customHeight="1">
@@ -4090,7 +4105,7 @@
         <v>306</v>
       </c>
       <c r="E74" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="75" ht="40" customHeight="1">
@@ -4107,24 +4122,24 @@
         <v>310</v>
       </c>
       <c r="E75" t="s">
-        <v>278</v>
+        <v>311</v>
       </c>
     </row>
     <row r="76" ht="40" customHeight="1">
       <c r="A76" t="s">
+        <v>312</v>
+      </c>
+      <c r="B76" t="s">
+        <v>313</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="E76" t="s">
         <v>311</v>
-      </c>
-      <c r="B76" t="s">
-        <v>312</v>
-      </c>
-      <c r="C76" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="D76" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="E76" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="77" ht="40" customHeight="1">
@@ -4138,10 +4153,95 @@
         <v>318</v>
       </c>
       <c r="D77" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="E77" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="78" ht="40" customHeight="1">
+      <c r="A78" t="s">
         <v>319</v>
       </c>
-      <c r="E77" t="s">
+      <c r="B78" t="s">
         <v>320</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="E78" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="79" ht="40" customHeight="1">
+      <c r="A79" t="s">
+        <v>323</v>
+      </c>
+      <c r="B79" t="s">
+        <v>324</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="E79" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="80" ht="40" customHeight="1">
+      <c r="A80" t="s">
+        <v>327</v>
+      </c>
+      <c r="B80" t="s">
+        <v>328</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="E80" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="81" ht="40" customHeight="1">
+      <c r="A81" t="s">
+        <v>331</v>
+      </c>
+      <c r="B81" t="s">
+        <v>332</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="E81" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="82" ht="40" customHeight="1">
+      <c r="A82" t="s">
+        <v>335</v>
+      </c>
+      <c r="B82" t="s">
+        <v>336</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="E82" t="s">
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -4169,16 +4269,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>321</v>
+        <v>340</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>341</v>
       </c>
       <c r="C1" t="s">
-        <v>322</v>
+        <v>342</v>
       </c>
       <c r="D1" t="s">
-        <v>12</v>
+        <v>343</v>
       </c>
       <c r="E1" t="s">
         <v>15</v>
@@ -4215,13 +4315,13 @@
     </row>
     <row r="3" ht="40" customHeight="1">
       <c r="A3" t="s">
-        <v>323</v>
+        <v>344</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>324</v>
+        <v>345</v>
       </c>
       <c r="D3" t="s">
         <v>22</v>
@@ -4230,21 +4330,21 @@
         <v>20</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>325</v>
+        <v>346</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>326</v>
+        <v>347</v>
       </c>
     </row>
     <row r="4" ht="40" customHeight="1">
       <c r="A4" t="s">
-        <v>323</v>
+        <v>344</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="D4" t="s">
         <v>22</v>
@@ -4253,21 +4353,21 @@
         <v>20</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>328</v>
+        <v>349</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>329</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5" ht="40" customHeight="1">
       <c r="A5" t="s">
-        <v>323</v>
+        <v>344</v>
       </c>
       <c r="B5" t="s">
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>330</v>
+        <v>351</v>
       </c>
       <c r="D5" t="s">
         <v>22</v>
@@ -4276,21 +4376,21 @@
         <v>20</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>331</v>
+        <v>352</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>331</v>
+        <v>352</v>
       </c>
     </row>
     <row r="6" ht="40" customHeight="1">
       <c r="A6" t="s">
-        <v>323</v>
+        <v>344</v>
       </c>
       <c r="B6" t="s">
         <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>332</v>
+        <v>353</v>
       </c>
       <c r="D6" t="s">
         <v>22</v>
@@ -4299,21 +4399,21 @@
         <v>20</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>333</v>
+        <v>354</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>333</v>
+        <v>354</v>
       </c>
     </row>
     <row r="7" ht="40" customHeight="1">
       <c r="A7" t="s">
-        <v>323</v>
+        <v>344</v>
       </c>
       <c r="B7" t="s">
         <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="D7" t="s">
         <v>22</v>
@@ -4322,21 +4422,21 @@
         <v>20</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>335</v>
+        <v>356</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>336</v>
+        <v>357</v>
       </c>
     </row>
     <row r="8" ht="40" customHeight="1">
       <c r="A8" t="s">
-        <v>337</v>
+        <v>358</v>
       </c>
       <c r="B8" t="s">
         <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>338</v>
+        <v>359</v>
       </c>
       <c r="D8" t="s">
         <v>22</v>
@@ -4345,21 +4445,21 @@
         <v>20</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>339</v>
+        <v>360</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>340</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9" ht="40" customHeight="1">
       <c r="A9" t="s">
-        <v>337</v>
+        <v>358</v>
       </c>
       <c r="B9" t="s">
         <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>341</v>
+        <v>362</v>
       </c>
       <c r="D9" t="s">
         <v>22</v>
@@ -4368,10 +4468,10 @@
         <v>20</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>342</v>
+        <v>363</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>343</v>
+        <v>364</v>
       </c>
     </row>
     <row r="10" ht="40" customHeight="1">
@@ -4428,7 +4528,7 @@
         <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>344</v>
+        <v>365</v>
       </c>
       <c r="D12" t="s">
         <v>34</v>
@@ -4451,7 +4551,7 @@
         <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>345</v>
+        <v>366</v>
       </c>
       <c r="D13" t="s">
         <v>34</v>
@@ -4460,21 +4560,21 @@
         <v>20</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>346</v>
+        <v>367</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>347</v>
+        <v>368</v>
       </c>
     </row>
     <row r="14" ht="40" customHeight="1">
       <c r="A14" t="s">
-        <v>348</v>
+        <v>369</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>349</v>
+        <v>370</v>
       </c>
       <c r="D14" t="s">
         <v>34</v>
@@ -4483,21 +4583,21 @@
         <v>20</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>350</v>
+        <v>371</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>351</v>
+        <v>372</v>
       </c>
     </row>
     <row r="15" ht="40" customHeight="1">
       <c r="A15" t="s">
-        <v>352</v>
+        <v>373</v>
       </c>
       <c r="B15" t="s">
         <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>353</v>
+        <v>374</v>
       </c>
       <c r="D15" t="s">
         <v>34</v>
@@ -4506,10 +4606,10 @@
         <v>20</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>354</v>
+        <v>375</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>355</v>
+        <v>376</v>
       </c>
     </row>
     <row r="16" ht="40" customHeight="1">
@@ -4566,7 +4666,7 @@
         <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>356</v>
+        <v>377</v>
       </c>
       <c r="D18" t="s">
         <v>46</v>
@@ -4575,10 +4675,10 @@
         <v>20</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>357</v>
+        <v>378</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
     </row>
     <row r="19" ht="40" customHeight="1">
@@ -4589,7 +4689,7 @@
         <v>45</v>
       </c>
       <c r="C19" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="D19" t="s">
         <v>46</v>
@@ -4598,10 +4698,10 @@
         <v>20</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>360</v>
+        <v>381</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>361</v>
+        <v>382</v>
       </c>
     </row>
     <row r="20" ht="40" customHeight="1">
@@ -4612,7 +4712,7 @@
         <v>45</v>
       </c>
       <c r="C20" t="s">
-        <v>362</v>
+        <v>383</v>
       </c>
       <c r="D20" t="s">
         <v>46</v>
@@ -4621,10 +4721,10 @@
         <v>20</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>363</v>
+        <v>384</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>364</v>
+        <v>385</v>
       </c>
     </row>
     <row r="21" ht="40" customHeight="1">
@@ -4635,7 +4735,7 @@
         <v>45</v>
       </c>
       <c r="C21" t="s">
-        <v>365</v>
+        <v>386</v>
       </c>
       <c r="D21" t="s">
         <v>46</v>
@@ -4644,10 +4744,10 @@
         <v>20</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>366</v>
+        <v>387</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>367</v>
+        <v>388</v>
       </c>
     </row>
     <row r="22" ht="40" customHeight="1">
@@ -4658,7 +4758,7 @@
         <v>45</v>
       </c>
       <c r="C22" t="s">
-        <v>368</v>
+        <v>389</v>
       </c>
       <c r="D22" t="s">
         <v>46</v>
@@ -4667,10 +4767,10 @@
         <v>20</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>369</v>
+        <v>390</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>370</v>
+        <v>391</v>
       </c>
     </row>
     <row r="23" ht="40" customHeight="1">
@@ -4681,7 +4781,7 @@
         <v>45</v>
       </c>
       <c r="C23" t="s">
-        <v>371</v>
+        <v>392</v>
       </c>
       <c r="D23" t="s">
         <v>46</v>
@@ -4690,10 +4790,10 @@
         <v>20</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>372</v>
+        <v>393</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>373</v>
+        <v>394</v>
       </c>
     </row>
     <row r="24" ht="40" customHeight="1">
@@ -4750,7 +4850,7 @@
         <v>57</v>
       </c>
       <c r="C26" t="s">
-        <v>374</v>
+        <v>395</v>
       </c>
       <c r="D26" t="s">
         <v>58</v>
@@ -4759,10 +4859,10 @@
         <v>20</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>375</v>
+        <v>396</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>376</v>
+        <v>397</v>
       </c>
     </row>
     <row r="27" ht="40" customHeight="1">
@@ -4782,10 +4882,10 @@
         <v>20</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>377</v>
+        <v>398</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
     </row>
     <row r="28" ht="40" customHeight="1">
@@ -4796,7 +4896,7 @@
         <v>61</v>
       </c>
       <c r="C28" t="s">
-        <v>379</v>
+        <v>400</v>
       </c>
       <c r="D28" t="s">
         <v>62</v>
@@ -4805,10 +4905,10 @@
         <v>20</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>380</v>
+        <v>401</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>381</v>
+        <v>402</v>
       </c>
     </row>
     <row r="29" ht="40" customHeight="1">
@@ -4828,10 +4928,10 @@
         <v>20</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>382</v>
+        <v>403</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>383</v>
+        <v>404</v>
       </c>
     </row>
     <row r="30" ht="40" customHeight="1">
@@ -4842,7 +4942,7 @@
         <v>65</v>
       </c>
       <c r="C30" t="s">
-        <v>384</v>
+        <v>405</v>
       </c>
       <c r="D30" t="s">
         <v>66</v>
@@ -4851,10 +4951,10 @@
         <v>20</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>385</v>
+        <v>406</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>386</v>
+        <v>407</v>
       </c>
     </row>
     <row r="31" ht="40" customHeight="1">
@@ -4865,7 +4965,7 @@
         <v>65</v>
       </c>
       <c r="C31" t="s">
-        <v>387</v>
+        <v>408</v>
       </c>
       <c r="D31" t="s">
         <v>66</v>
@@ -4874,10 +4974,10 @@
         <v>20</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>388</v>
+        <v>409</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>388</v>
+        <v>409</v>
       </c>
     </row>
     <row r="32" ht="40" customHeight="1">
@@ -4888,7 +4988,7 @@
         <v>65</v>
       </c>
       <c r="C32" t="s">
-        <v>389</v>
+        <v>410</v>
       </c>
       <c r="D32" t="s">
         <v>66</v>
@@ -4897,10 +4997,10 @@
         <v>20</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>390</v>
+        <v>411</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>390</v>
+        <v>411</v>
       </c>
     </row>
     <row r="33" ht="40" customHeight="1">
@@ -4911,7 +5011,7 @@
         <v>65</v>
       </c>
       <c r="C33" t="s">
-        <v>391</v>
+        <v>412</v>
       </c>
       <c r="D33" t="s">
         <v>66</v>
@@ -4934,7 +5034,7 @@
         <v>65</v>
       </c>
       <c r="C34" t="s">
-        <v>392</v>
+        <v>413</v>
       </c>
       <c r="D34" t="s">
         <v>66</v>
@@ -4943,10 +5043,10 @@
         <v>20</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>393</v>
+        <v>414</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>394</v>
+        <v>415</v>
       </c>
     </row>
     <row r="35" ht="40" customHeight="1">
@@ -4957,7 +5057,7 @@
         <v>65</v>
       </c>
       <c r="C35" t="s">
-        <v>395</v>
+        <v>416</v>
       </c>
       <c r="D35" t="s">
         <v>66</v>
@@ -4966,10 +5066,10 @@
         <v>20</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>396</v>
+        <v>417</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>397</v>
+        <v>418</v>
       </c>
     </row>
     <row r="36" ht="40" customHeight="1">
@@ -4980,7 +5080,7 @@
         <v>65</v>
       </c>
       <c r="C36" t="s">
-        <v>398</v>
+        <v>419</v>
       </c>
       <c r="D36" t="s">
         <v>66</v>
@@ -4989,10 +5089,10 @@
         <v>20</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>399</v>
+        <v>420</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>399</v>
+        <v>420</v>
       </c>
     </row>
     <row r="37" ht="40" customHeight="1">
@@ -5003,7 +5103,7 @@
         <v>65</v>
       </c>
       <c r="C37" t="s">
-        <v>400</v>
+        <v>421</v>
       </c>
       <c r="D37" t="s">
         <v>66</v>
@@ -5012,10 +5112,10 @@
         <v>20</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>401</v>
+        <v>422</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>401</v>
+        <v>422</v>
       </c>
     </row>
     <row r="38" ht="40" customHeight="1">
@@ -5026,7 +5126,7 @@
         <v>65</v>
       </c>
       <c r="C38" t="s">
-        <v>402</v>
+        <v>423</v>
       </c>
       <c r="D38" t="s">
         <v>66</v>
@@ -5035,10 +5135,10 @@
         <v>20</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>403</v>
+        <v>424</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>403</v>
+        <v>424</v>
       </c>
     </row>
     <row r="39" ht="40" customHeight="1">
@@ -5049,7 +5149,7 @@
         <v>65</v>
       </c>
       <c r="C39" t="s">
-        <v>404</v>
+        <v>425</v>
       </c>
       <c r="D39" t="s">
         <v>66</v>
@@ -5058,10 +5158,10 @@
         <v>20</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>405</v>
+        <v>426</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>405</v>
+        <v>426</v>
       </c>
     </row>
     <row r="40" ht="40" customHeight="1">
@@ -5072,7 +5172,7 @@
         <v>65</v>
       </c>
       <c r="C40" t="s">
-        <v>406</v>
+        <v>427</v>
       </c>
       <c r="D40" t="s">
         <v>66</v>
@@ -5081,10 +5181,10 @@
         <v>20</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>407</v>
+        <v>428</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>408</v>
+        <v>429</v>
       </c>
     </row>
     <row r="41" ht="40" customHeight="1">
@@ -5095,7 +5195,7 @@
         <v>65</v>
       </c>
       <c r="C41" t="s">
-        <v>409</v>
+        <v>430</v>
       </c>
       <c r="D41" t="s">
         <v>66</v>
@@ -5104,10 +5204,10 @@
         <v>20</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>410</v>
+        <v>431</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>410</v>
+        <v>431</v>
       </c>
     </row>
     <row r="42" ht="40" customHeight="1">
@@ -5118,7 +5218,7 @@
         <v>65</v>
       </c>
       <c r="C42" t="s">
-        <v>411</v>
+        <v>432</v>
       </c>
       <c r="D42" t="s">
         <v>66</v>
@@ -5127,10 +5227,10 @@
         <v>20</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>412</v>
+        <v>433</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>412</v>
+        <v>433</v>
       </c>
     </row>
     <row r="43" ht="40" customHeight="1">
@@ -5141,7 +5241,7 @@
         <v>65</v>
       </c>
       <c r="C43" t="s">
-        <v>413</v>
+        <v>434</v>
       </c>
       <c r="D43" t="s">
         <v>66</v>
@@ -5150,10 +5250,10 @@
         <v>20</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>414</v>
+        <v>435</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>414</v>
+        <v>435</v>
       </c>
     </row>
     <row r="44" ht="40" customHeight="1">
@@ -5164,7 +5264,7 @@
         <v>65</v>
       </c>
       <c r="C44" t="s">
-        <v>415</v>
+        <v>436</v>
       </c>
       <c r="D44" t="s">
         <v>66</v>
@@ -5173,10 +5273,10 @@
         <v>20</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>416</v>
+        <v>437</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>416</v>
+        <v>437</v>
       </c>
     </row>
     <row r="45" ht="40" customHeight="1">
@@ -5187,7 +5287,7 @@
         <v>65</v>
       </c>
       <c r="C45" t="s">
-        <v>417</v>
+        <v>438</v>
       </c>
       <c r="D45" t="s">
         <v>66</v>
@@ -5196,10 +5296,10 @@
         <v>20</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>418</v>
+        <v>439</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>419</v>
+        <v>440</v>
       </c>
     </row>
     <row r="46" ht="40" customHeight="1">
@@ -5210,7 +5310,7 @@
         <v>65</v>
       </c>
       <c r="C46" t="s">
-        <v>420</v>
+        <v>441</v>
       </c>
       <c r="D46" t="s">
         <v>66</v>
@@ -5219,10 +5319,10 @@
         <v>20</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>421</v>
+        <v>442</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>421</v>
+        <v>442</v>
       </c>
     </row>
     <row r="47" ht="40" customHeight="1">
@@ -5233,7 +5333,7 @@
         <v>65</v>
       </c>
       <c r="C47" t="s">
-        <v>422</v>
+        <v>443</v>
       </c>
       <c r="D47" t="s">
         <v>66</v>
@@ -5242,10 +5342,10 @@
         <v>20</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>423</v>
+        <v>444</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>423</v>
+        <v>444</v>
       </c>
     </row>
     <row r="48" ht="40" customHeight="1">
@@ -5256,7 +5356,7 @@
         <v>65</v>
       </c>
       <c r="C48" t="s">
-        <v>424</v>
+        <v>445</v>
       </c>
       <c r="D48" t="s">
         <v>66</v>
@@ -5265,10 +5365,10 @@
         <v>20</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>425</v>
+        <v>446</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>425</v>
+        <v>446</v>
       </c>
     </row>
     <row r="49" ht="40" customHeight="1">
@@ -5279,7 +5379,7 @@
         <v>65</v>
       </c>
       <c r="C49" t="s">
-        <v>426</v>
+        <v>447</v>
       </c>
       <c r="D49" t="s">
         <v>66</v>
@@ -5288,10 +5388,10 @@
         <v>20</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>427</v>
+        <v>448</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>427</v>
+        <v>448</v>
       </c>
     </row>
     <row r="50" ht="40" customHeight="1">
@@ -5302,7 +5402,7 @@
         <v>65</v>
       </c>
       <c r="C50" t="s">
-        <v>428</v>
+        <v>449</v>
       </c>
       <c r="D50" t="s">
         <v>66</v>
@@ -5311,10 +5411,10 @@
         <v>20</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>429</v>
+        <v>450</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>429</v>
+        <v>450</v>
       </c>
     </row>
     <row r="51" ht="40" customHeight="1">
@@ -5325,7 +5425,7 @@
         <v>65</v>
       </c>
       <c r="C51" t="s">
-        <v>430</v>
+        <v>451</v>
       </c>
       <c r="D51" t="s">
         <v>66</v>
@@ -5334,10 +5434,10 @@
         <v>20</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>431</v>
+        <v>452</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>431</v>
+        <v>452</v>
       </c>
     </row>
     <row r="52" ht="40" customHeight="1">
@@ -5348,7 +5448,7 @@
         <v>65</v>
       </c>
       <c r="C52" t="s">
-        <v>432</v>
+        <v>453</v>
       </c>
       <c r="D52" t="s">
         <v>66</v>
@@ -5357,10 +5457,10 @@
         <v>20</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>433</v>
+        <v>454</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>434</v>
+        <v>455</v>
       </c>
     </row>
     <row r="53" ht="40" customHeight="1">
@@ -5371,7 +5471,7 @@
         <v>65</v>
       </c>
       <c r="C53" t="s">
-        <v>435</v>
+        <v>456</v>
       </c>
       <c r="D53" t="s">
         <v>66</v>
@@ -5380,10 +5480,10 @@
         <v>20</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>436</v>
+        <v>457</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>437</v>
+        <v>458</v>
       </c>
     </row>
     <row r="54" ht="40" customHeight="1">
@@ -5394,7 +5494,7 @@
         <v>65</v>
       </c>
       <c r="C54" t="s">
-        <v>438</v>
+        <v>459</v>
       </c>
       <c r="D54" t="s">
         <v>66</v>
@@ -5403,10 +5503,10 @@
         <v>20</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>439</v>
+        <v>460</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>440</v>
+        <v>461</v>
       </c>
     </row>
     <row r="55" ht="40" customHeight="1">
@@ -5417,7 +5517,7 @@
         <v>65</v>
       </c>
       <c r="C55" t="s">
-        <v>441</v>
+        <v>462</v>
       </c>
       <c r="D55" t="s">
         <v>66</v>
@@ -5426,10 +5526,10 @@
         <v>20</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>442</v>
+        <v>463</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>443</v>
+        <v>464</v>
       </c>
     </row>
     <row r="56" ht="40" customHeight="1">
@@ -5440,7 +5540,7 @@
         <v>65</v>
       </c>
       <c r="C56" t="s">
-        <v>444</v>
+        <v>465</v>
       </c>
       <c r="D56" t="s">
         <v>66</v>
@@ -5449,10 +5549,10 @@
         <v>20</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>445</v>
+        <v>466</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>446</v>
+        <v>467</v>
       </c>
     </row>
     <row r="57" ht="40" customHeight="1">
@@ -5463,7 +5563,7 @@
         <v>65</v>
       </c>
       <c r="C57" t="s">
-        <v>447</v>
+        <v>468</v>
       </c>
       <c r="D57" t="s">
         <v>66</v>
@@ -5472,10 +5572,10 @@
         <v>20</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>448</v>
+        <v>469</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>448</v>
+        <v>469</v>
       </c>
     </row>
     <row r="58" ht="40" customHeight="1">
@@ -5486,7 +5586,7 @@
         <v>65</v>
       </c>
       <c r="C58" t="s">
-        <v>449</v>
+        <v>470</v>
       </c>
       <c r="D58" t="s">
         <v>66</v>
@@ -5495,10 +5595,10 @@
         <v>20</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>450</v>
+        <v>471</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>451</v>
+        <v>472</v>
       </c>
     </row>
     <row r="59" ht="40" customHeight="1">
@@ -5518,10 +5618,10 @@
         <v>73</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>452</v>
+        <v>473</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>452</v>
+        <v>473</v>
       </c>
     </row>
     <row r="60" ht="40" customHeight="1">
@@ -5532,7 +5632,7 @@
         <v>69</v>
       </c>
       <c r="C60" t="s">
-        <v>453</v>
+        <v>474</v>
       </c>
       <c r="D60" t="s">
         <v>70</v>
@@ -5541,10 +5641,10 @@
         <v>73</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>454</v>
+        <v>475</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>455</v>
+        <v>476</v>
       </c>
     </row>
     <row r="61" ht="40" customHeight="1">
@@ -5555,7 +5655,7 @@
         <v>69</v>
       </c>
       <c r="C61" t="s">
-        <v>456</v>
+        <v>477</v>
       </c>
       <c r="D61" t="s">
         <v>70</v>
@@ -5564,10 +5664,10 @@
         <v>73</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>457</v>
+        <v>478</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>458</v>
+        <v>479</v>
       </c>
     </row>
     <row r="62" ht="40" customHeight="1">
@@ -5578,7 +5678,7 @@
         <v>69</v>
       </c>
       <c r="C62" t="s">
-        <v>459</v>
+        <v>480</v>
       </c>
       <c r="D62" t="s">
         <v>70</v>
@@ -5587,10 +5687,10 @@
         <v>73</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>460</v>
+        <v>481</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>461</v>
+        <v>482</v>
       </c>
     </row>
     <row r="63" ht="40" customHeight="1">
@@ -5739,7 +5839,7 @@
         <v>98</v>
       </c>
       <c r="C69" t="s">
-        <v>462</v>
+        <v>483</v>
       </c>
       <c r="D69" t="s">
         <v>99</v>
@@ -5748,10 +5848,10 @@
         <v>73</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>463</v>
+        <v>484</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>464</v>
+        <v>485</v>
       </c>
     </row>
     <row r="70" ht="40" customHeight="1">
@@ -5762,7 +5862,7 @@
         <v>98</v>
       </c>
       <c r="C70" t="s">
-        <v>465</v>
+        <v>486</v>
       </c>
       <c r="D70" t="s">
         <v>99</v>
@@ -5771,10 +5871,10 @@
         <v>73</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>466</v>
+        <v>487</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>467</v>
+        <v>488</v>
       </c>
     </row>
     <row r="71" ht="40" customHeight="1">
@@ -5802,13 +5902,13 @@
     </row>
     <row r="72" ht="40" customHeight="1">
       <c r="A72" t="s">
-        <v>468</v>
+        <v>489</v>
       </c>
       <c r="B72" t="s">
         <v>106</v>
       </c>
       <c r="C72" t="s">
-        <v>469</v>
+        <v>490</v>
       </c>
       <c r="D72" t="s">
         <v>107</v>
@@ -5817,21 +5917,21 @@
         <v>73</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>470</v>
+        <v>491</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>471</v>
+        <v>492</v>
       </c>
     </row>
     <row r="73" ht="40" customHeight="1">
       <c r="A73" t="s">
-        <v>472</v>
+        <v>493</v>
       </c>
       <c r="B73" t="s">
         <v>106</v>
       </c>
       <c r="C73" t="s">
-        <v>473</v>
+        <v>494</v>
       </c>
       <c r="D73" t="s">
         <v>107</v>
@@ -5840,10 +5940,10 @@
         <v>73</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>474</v>
+        <v>495</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>475</v>
+        <v>496</v>
       </c>
     </row>
     <row r="74" ht="40" customHeight="1">
@@ -5940,13 +6040,13 @@
     </row>
     <row r="78" ht="40" customHeight="1">
       <c r="A78" t="s">
-        <v>476</v>
+        <v>497</v>
       </c>
       <c r="B78" t="s">
         <v>126</v>
       </c>
       <c r="C78" t="s">
-        <v>477</v>
+        <v>498</v>
       </c>
       <c r="D78" t="s">
         <v>127</v>
@@ -5955,21 +6055,21 @@
         <v>73</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>478</v>
+        <v>499</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>479</v>
+        <v>500</v>
       </c>
     </row>
     <row r="79" ht="40" customHeight="1">
       <c r="A79" t="s">
-        <v>480</v>
+        <v>501</v>
       </c>
       <c r="B79" t="s">
         <v>126</v>
       </c>
       <c r="C79" t="s">
-        <v>481</v>
+        <v>502</v>
       </c>
       <c r="D79" t="s">
         <v>127</v>
@@ -5978,21 +6078,21 @@
         <v>73</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>482</v>
+        <v>503</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>483</v>
+        <v>504</v>
       </c>
     </row>
     <row r="80" ht="40" customHeight="1">
       <c r="A80" t="s">
-        <v>484</v>
+        <v>505</v>
       </c>
       <c r="B80" t="s">
         <v>130</v>
       </c>
       <c r="C80" t="s">
-        <v>485</v>
+        <v>506</v>
       </c>
       <c r="D80" t="s">
         <v>131</v>
@@ -6001,21 +6101,21 @@
         <v>73</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>486</v>
+        <v>507</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>486</v>
+        <v>507</v>
       </c>
     </row>
     <row r="81" ht="40" customHeight="1">
       <c r="A81" t="s">
-        <v>487</v>
+        <v>508</v>
       </c>
       <c r="B81" t="s">
         <v>130</v>
       </c>
       <c r="C81" t="s">
-        <v>488</v>
+        <v>509</v>
       </c>
       <c r="D81" t="s">
         <v>131</v>
@@ -6024,21 +6124,21 @@
         <v>73</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>489</v>
+        <v>510</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>490</v>
+        <v>511</v>
       </c>
     </row>
     <row r="82" ht="40" customHeight="1">
       <c r="A82" t="s">
-        <v>491</v>
+        <v>512</v>
       </c>
       <c r="B82" t="s">
         <v>130</v>
       </c>
       <c r="C82" t="s">
-        <v>492</v>
+        <v>513</v>
       </c>
       <c r="D82" t="s">
         <v>131</v>
@@ -6047,10 +6147,10 @@
         <v>73</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>493</v>
+        <v>514</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>494</v>
+        <v>515</v>
       </c>
     </row>
     <row r="83" ht="40" customHeight="1">
@@ -6084,7 +6184,7 @@
         <v>138</v>
       </c>
       <c r="C84" t="s">
-        <v>495</v>
+        <v>516</v>
       </c>
       <c r="D84" t="s">
         <v>139</v>
@@ -6093,10 +6193,10 @@
         <v>73</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>496</v>
+        <v>517</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>497</v>
+        <v>518</v>
       </c>
     </row>
     <row r="85" ht="40" customHeight="1">
@@ -6107,7 +6207,7 @@
         <v>138</v>
       </c>
       <c r="C85" t="s">
-        <v>498</v>
+        <v>519</v>
       </c>
       <c r="D85" t="s">
         <v>139</v>
@@ -6116,10 +6216,10 @@
         <v>73</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>499</v>
+        <v>520</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>500</v>
+        <v>521</v>
       </c>
     </row>
     <row r="86" ht="40" customHeight="1">
@@ -6130,7 +6230,7 @@
         <v>138</v>
       </c>
       <c r="C86" t="s">
-        <v>501</v>
+        <v>522</v>
       </c>
       <c r="D86" t="s">
         <v>139</v>
@@ -6139,10 +6239,10 @@
         <v>73</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>502</v>
+        <v>523</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>503</v>
+        <v>524</v>
       </c>
     </row>
     <row r="87" ht="40" customHeight="1">
@@ -6153,7 +6253,7 @@
         <v>138</v>
       </c>
       <c r="C87" t="s">
-        <v>504</v>
+        <v>525</v>
       </c>
       <c r="D87" t="s">
         <v>139</v>
@@ -6162,10 +6262,10 @@
         <v>73</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>505</v>
+        <v>526</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>506</v>
+        <v>527</v>
       </c>
     </row>
     <row r="88" ht="40" customHeight="1">
@@ -6176,7 +6276,7 @@
         <v>138</v>
       </c>
       <c r="C88" t="s">
-        <v>507</v>
+        <v>528</v>
       </c>
       <c r="D88" t="s">
         <v>139</v>
@@ -6185,10 +6285,10 @@
         <v>73</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>508</v>
+        <v>529</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>508</v>
+        <v>529</v>
       </c>
     </row>
     <row r="89" ht="40" customHeight="1">
@@ -6208,10 +6308,10 @@
         <v>73</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>509</v>
+        <v>530</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>510</v>
+        <v>531</v>
       </c>
     </row>
     <row r="90" ht="40" customHeight="1">
@@ -6452,7 +6552,7 @@
         <v>181</v>
       </c>
       <c r="C100" t="s">
-        <v>511</v>
+        <v>532</v>
       </c>
       <c r="D100" t="s">
         <v>182</v>
@@ -6461,10 +6561,10 @@
         <v>150</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>512</v>
+        <v>533</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>513</v>
+        <v>534</v>
       </c>
     </row>
     <row r="101" ht="40" customHeight="1">
@@ -6484,10 +6584,10 @@
         <v>150</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>514</v>
+        <v>535</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>515</v>
+        <v>536</v>
       </c>
     </row>
     <row r="102" ht="40" customHeight="1">
@@ -6521,7 +6621,7 @@
         <v>190</v>
       </c>
       <c r="C103" t="s">
-        <v>516</v>
+        <v>537</v>
       </c>
       <c r="D103" t="s">
         <v>191</v>
@@ -6530,10 +6630,10 @@
         <v>189</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>517</v>
+        <v>538</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>517</v>
+        <v>538</v>
       </c>
     </row>
     <row r="104" ht="40" customHeight="1">
@@ -6544,7 +6644,7 @@
         <v>190</v>
       </c>
       <c r="C104" t="s">
-        <v>518</v>
+        <v>539</v>
       </c>
       <c r="D104" t="s">
         <v>191</v>
@@ -6553,10 +6653,10 @@
         <v>189</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>519</v>
+        <v>540</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>520</v>
+        <v>541</v>
       </c>
     </row>
     <row r="105" ht="40" customHeight="1">
@@ -6567,7 +6667,7 @@
         <v>190</v>
       </c>
       <c r="C105" t="s">
-        <v>521</v>
+        <v>542</v>
       </c>
       <c r="D105" t="s">
         <v>191</v>
@@ -6576,10 +6676,10 @@
         <v>189</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>522</v>
+        <v>543</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>523</v>
+        <v>544</v>
       </c>
     </row>
     <row r="106" ht="40" customHeight="1">
@@ -6607,13 +6707,13 @@
     </row>
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="s">
-        <v>524</v>
+        <v>545</v>
       </c>
       <c r="B107" t="s">
         <v>197</v>
       </c>
       <c r="C107" t="s">
-        <v>525</v>
+        <v>546</v>
       </c>
       <c r="D107" t="s">
         <v>198</v>
@@ -6622,21 +6722,21 @@
         <v>189</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>526</v>
+        <v>547</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>527</v>
+        <v>548</v>
       </c>
     </row>
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="s">
-        <v>528</v>
+        <v>549</v>
       </c>
       <c r="B108" t="s">
         <v>197</v>
       </c>
       <c r="C108" t="s">
-        <v>529</v>
+        <v>550</v>
       </c>
       <c r="D108" t="s">
         <v>198</v>
@@ -6645,21 +6745,21 @@
         <v>189</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>530</v>
+        <v>551</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>531</v>
+        <v>552</v>
       </c>
     </row>
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="s">
-        <v>532</v>
+        <v>553</v>
       </c>
       <c r="B109" t="s">
         <v>197</v>
       </c>
       <c r="C109" t="s">
-        <v>533</v>
+        <v>554</v>
       </c>
       <c r="D109" t="s">
         <v>198</v>
@@ -6668,21 +6768,21 @@
         <v>189</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>534</v>
+        <v>555</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>535</v>
+        <v>556</v>
       </c>
     </row>
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="s">
-        <v>536</v>
+        <v>557</v>
       </c>
       <c r="B110" t="s">
         <v>197</v>
       </c>
       <c r="C110" t="s">
-        <v>537</v>
+        <v>558</v>
       </c>
       <c r="D110" t="s">
         <v>198</v>
@@ -6691,21 +6791,21 @@
         <v>189</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>538</v>
+        <v>559</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>539</v>
+        <v>560</v>
       </c>
     </row>
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="s">
-        <v>540</v>
+        <v>561</v>
       </c>
       <c r="B111" t="s">
         <v>197</v>
       </c>
       <c r="C111" t="s">
-        <v>541</v>
+        <v>562</v>
       </c>
       <c r="D111" t="s">
         <v>198</v>
@@ -6714,21 +6814,21 @@
         <v>189</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>542</v>
+        <v>563</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>543</v>
+        <v>564</v>
       </c>
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="s">
-        <v>544</v>
+        <v>565</v>
       </c>
       <c r="B112" t="s">
         <v>197</v>
       </c>
       <c r="C112" t="s">
-        <v>545</v>
+        <v>566</v>
       </c>
       <c r="D112" t="s">
         <v>198</v>
@@ -6737,21 +6837,21 @@
         <v>189</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>546</v>
+        <v>567</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>546</v>
+        <v>567</v>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="s">
-        <v>547</v>
+        <v>568</v>
       </c>
       <c r="B113" t="s">
         <v>197</v>
       </c>
       <c r="C113" t="s">
-        <v>548</v>
+        <v>569</v>
       </c>
       <c r="D113" t="s">
         <v>198</v>
@@ -6760,21 +6860,21 @@
         <v>189</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>549</v>
+        <v>570</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>549</v>
+        <v>570</v>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="s">
-        <v>550</v>
+        <v>571</v>
       </c>
       <c r="B114" t="s">
         <v>197</v>
       </c>
       <c r="C114" t="s">
-        <v>551</v>
+        <v>572</v>
       </c>
       <c r="D114" t="s">
         <v>198</v>
@@ -6783,21 +6883,21 @@
         <v>189</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>552</v>
+        <v>573</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>552</v>
+        <v>573</v>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="s">
-        <v>553</v>
+        <v>574</v>
       </c>
       <c r="B115" t="s">
         <v>197</v>
       </c>
       <c r="C115" t="s">
-        <v>554</v>
+        <v>575</v>
       </c>
       <c r="D115" t="s">
         <v>198</v>
@@ -6806,21 +6906,21 @@
         <v>189</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>555</v>
+        <v>576</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>556</v>
+        <v>577</v>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="s">
-        <v>557</v>
+        <v>578</v>
       </c>
       <c r="B116" t="s">
         <v>197</v>
       </c>
       <c r="C116" t="s">
-        <v>558</v>
+        <v>579</v>
       </c>
       <c r="D116" t="s">
         <v>198</v>
@@ -6829,21 +6929,21 @@
         <v>189</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>559</v>
+        <v>580</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>560</v>
+        <v>581</v>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="s">
-        <v>561</v>
+        <v>582</v>
       </c>
       <c r="B117" t="s">
         <v>197</v>
       </c>
       <c r="C117" t="s">
-        <v>562</v>
+        <v>583</v>
       </c>
       <c r="D117" t="s">
         <v>198</v>
@@ -6852,21 +6952,21 @@
         <v>189</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>563</v>
+        <v>584</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>564</v>
+        <v>585</v>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="s">
-        <v>565</v>
+        <v>586</v>
       </c>
       <c r="B118" t="s">
         <v>201</v>
       </c>
       <c r="C118" t="s">
-        <v>566</v>
+        <v>587</v>
       </c>
       <c r="D118" t="s">
         <v>202</v>
@@ -6875,21 +6975,21 @@
         <v>189</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>567</v>
+        <v>588</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>568</v>
+        <v>589</v>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="s">
-        <v>569</v>
+        <v>590</v>
       </c>
       <c r="B119" t="s">
         <v>201</v>
       </c>
       <c r="C119" t="s">
-        <v>570</v>
+        <v>591</v>
       </c>
       <c r="D119" t="s">
         <v>202</v>
@@ -6898,21 +6998,21 @@
         <v>189</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>571</v>
+        <v>592</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>572</v>
+        <v>593</v>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="s">
-        <v>573</v>
+        <v>594</v>
       </c>
       <c r="B120" t="s">
         <v>201</v>
       </c>
       <c r="C120" t="s">
-        <v>574</v>
+        <v>595</v>
       </c>
       <c r="D120" t="s">
         <v>202</v>
@@ -6921,21 +7021,21 @@
         <v>189</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>575</v>
+        <v>596</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>575</v>
+        <v>596</v>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="s">
-        <v>576</v>
+        <v>597</v>
       </c>
       <c r="B121" t="s">
         <v>201</v>
       </c>
       <c r="C121" t="s">
-        <v>577</v>
+        <v>598</v>
       </c>
       <c r="D121" t="s">
         <v>202</v>
@@ -6944,10 +7044,10 @@
         <v>189</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>578</v>
+        <v>599</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>578</v>
+        <v>599</v>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
@@ -6958,7 +7058,7 @@
         <v>205</v>
       </c>
       <c r="C122" t="s">
-        <v>579</v>
+        <v>600</v>
       </c>
       <c r="D122" t="s">
         <v>206</v>
@@ -6967,10 +7067,10 @@
         <v>189</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>580</v>
+        <v>601</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>581</v>
+        <v>602</v>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
@@ -6981,7 +7081,7 @@
         <v>205</v>
       </c>
       <c r="C123" t="s">
-        <v>582</v>
+        <v>603</v>
       </c>
       <c r="D123" t="s">
         <v>206</v>
@@ -6990,10 +7090,10 @@
         <v>189</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>583</v>
+        <v>604</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>583</v>
+        <v>604</v>
       </c>
     </row>
     <row r="124" ht="40" customHeight="1">
@@ -7004,7 +7104,7 @@
         <v>205</v>
       </c>
       <c r="C124" t="s">
-        <v>584</v>
+        <v>605</v>
       </c>
       <c r="D124" t="s">
         <v>206</v>
@@ -7013,10 +7113,10 @@
         <v>189</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>585</v>
+        <v>606</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>585</v>
+        <v>606</v>
       </c>
     </row>
     <row r="125" ht="40" customHeight="1">
@@ -7027,7 +7127,7 @@
         <v>205</v>
       </c>
       <c r="C125" t="s">
-        <v>586</v>
+        <v>607</v>
       </c>
       <c r="D125" t="s">
         <v>206</v>
@@ -7036,10 +7136,10 @@
         <v>189</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>587</v>
+        <v>608</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>587</v>
+        <v>608</v>
       </c>
     </row>
     <row r="126" ht="40" customHeight="1">
@@ -7059,10 +7159,10 @@
         <v>189</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>588</v>
+        <v>609</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>589</v>
+        <v>610</v>
       </c>
     </row>
     <row r="127" ht="40" customHeight="1">
@@ -7096,7 +7196,7 @@
         <v>213</v>
       </c>
       <c r="C128" t="s">
-        <v>590</v>
+        <v>611</v>
       </c>
       <c r="D128" t="s">
         <v>214</v>
@@ -7105,10 +7205,10 @@
         <v>189</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>591</v>
+        <v>612</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>592</v>
+        <v>613</v>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
@@ -7119,7 +7219,7 @@
         <v>213</v>
       </c>
       <c r="C129" t="s">
-        <v>593</v>
+        <v>614</v>
       </c>
       <c r="D129" t="s">
         <v>214</v>
@@ -7128,10 +7228,10 @@
         <v>189</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>594</v>
+        <v>615</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>595</v>
+        <v>616</v>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
@@ -7142,7 +7242,7 @@
         <v>213</v>
       </c>
       <c r="C130" t="s">
-        <v>596</v>
+        <v>617</v>
       </c>
       <c r="D130" t="s">
         <v>214</v>
@@ -7151,10 +7251,10 @@
         <v>189</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>597</v>
+        <v>618</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>598</v>
+        <v>619</v>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
@@ -7165,7 +7265,7 @@
         <v>213</v>
       </c>
       <c r="C131" t="s">
-        <v>599</v>
+        <v>620</v>
       </c>
       <c r="D131" t="s">
         <v>214</v>
@@ -7174,10 +7274,10 @@
         <v>189</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>600</v>
+        <v>621</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>600</v>
+        <v>621</v>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
@@ -7188,7 +7288,7 @@
         <v>213</v>
       </c>
       <c r="C132" t="s">
-        <v>601</v>
+        <v>622</v>
       </c>
       <c r="D132" t="s">
         <v>214</v>
@@ -7197,10 +7297,10 @@
         <v>189</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>602</v>
+        <v>623</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>603</v>
+        <v>624</v>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
@@ -7211,7 +7311,7 @@
         <v>213</v>
       </c>
       <c r="C133" t="s">
-        <v>604</v>
+        <v>625</v>
       </c>
       <c r="D133" t="s">
         <v>214</v>
@@ -7220,10 +7320,10 @@
         <v>189</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>605</v>
+        <v>626</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>606</v>
+        <v>627</v>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
@@ -7234,7 +7334,7 @@
         <v>213</v>
       </c>
       <c r="C134" t="s">
-        <v>607</v>
+        <v>628</v>
       </c>
       <c r="D134" t="s">
         <v>214</v>
@@ -7243,10 +7343,10 @@
         <v>189</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>608</v>
+        <v>629</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>609</v>
+        <v>630</v>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
@@ -7257,7 +7357,7 @@
         <v>213</v>
       </c>
       <c r="C135" t="s">
-        <v>610</v>
+        <v>631</v>
       </c>
       <c r="D135" t="s">
         <v>214</v>
@@ -7266,21 +7366,21 @@
         <v>189</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>611</v>
+        <v>632</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>612</v>
+        <v>633</v>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="s">
-        <v>613</v>
+        <v>634</v>
       </c>
       <c r="B136" t="s">
         <v>217</v>
       </c>
       <c r="C136" t="s">
-        <v>614</v>
+        <v>635</v>
       </c>
       <c r="D136" t="s">
         <v>218</v>
@@ -7289,21 +7389,21 @@
         <v>189</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>615</v>
+        <v>636</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>616</v>
+        <v>637</v>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="s">
-        <v>617</v>
+        <v>638</v>
       </c>
       <c r="B137" t="s">
         <v>217</v>
       </c>
       <c r="C137" t="s">
-        <v>618</v>
+        <v>639</v>
       </c>
       <c r="D137" t="s">
         <v>218</v>
@@ -7312,21 +7412,21 @@
         <v>189</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>619</v>
+        <v>640</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>620</v>
+        <v>641</v>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="s">
-        <v>621</v>
+        <v>642</v>
       </c>
       <c r="B138" t="s">
         <v>217</v>
       </c>
       <c r="C138" t="s">
-        <v>622</v>
+        <v>643</v>
       </c>
       <c r="D138" t="s">
         <v>218</v>
@@ -7335,10 +7435,10 @@
         <v>189</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>623</v>
+        <v>644</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>624</v>
+        <v>645</v>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
@@ -7372,7 +7472,7 @@
         <v>225</v>
       </c>
       <c r="C140" t="s">
-        <v>625</v>
+        <v>226</v>
       </c>
       <c r="D140" t="s">
         <v>226</v>
@@ -7381,746 +7481,746 @@
         <v>189</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>626</v>
+        <v>227</v>
       </c>
       <c r="G140" s="4" t="s">
-        <v>627</v>
+        <v>228</v>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B141" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C141" t="s">
-        <v>628</v>
+        <v>230</v>
       </c>
       <c r="D141" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E141" t="s">
         <v>189</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>629</v>
+        <v>231</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>630</v>
+        <v>231</v>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B142" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="C142" t="s">
-        <v>631</v>
+        <v>233</v>
       </c>
       <c r="D142" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="E142" t="s">
         <v>189</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>632</v>
+        <v>234</v>
       </c>
       <c r="G142" s="4" t="s">
-        <v>632</v>
+        <v>235</v>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="B143" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="C143" t="s">
-        <v>633</v>
+        <v>237</v>
       </c>
       <c r="D143" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="E143" t="s">
         <v>189</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>634</v>
+        <v>238</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>635</v>
+        <v>239</v>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="B144" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="C144" t="s">
-        <v>636</v>
+        <v>241</v>
       </c>
       <c r="D144" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="E144" t="s">
         <v>189</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>637</v>
+        <v>242</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>638</v>
+        <v>243</v>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="s">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="B145" t="s">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="C145" t="s">
-        <v>639</v>
+        <v>245</v>
       </c>
       <c r="D145" t="s">
-        <v>226</v>
+        <v>245</v>
       </c>
       <c r="E145" t="s">
         <v>189</v>
       </c>
       <c r="F145" s="4" t="s">
-        <v>640</v>
+        <v>246</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>641</v>
+        <v>247</v>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="s">
-        <v>229</v>
+        <v>248</v>
       </c>
       <c r="B146" t="s">
-        <v>229</v>
+        <v>248</v>
       </c>
       <c r="C146" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D146" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="E146" t="s">
         <v>189</v>
       </c>
       <c r="F146" s="4" t="s">
-        <v>231</v>
+        <v>250</v>
       </c>
       <c r="G146" s="4" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="s">
-        <v>233</v>
+        <v>252</v>
       </c>
       <c r="B147" t="s">
-        <v>233</v>
+        <v>252</v>
       </c>
       <c r="C147" t="s">
-        <v>234</v>
+        <v>253</v>
       </c>
       <c r="D147" t="s">
-        <v>234</v>
+        <v>253</v>
       </c>
       <c r="E147" t="s">
         <v>189</v>
       </c>
       <c r="F147" s="4" t="s">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>235</v>
+        <v>255</v>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="s">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="B148" t="s">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="C148" t="s">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="D148" t="s">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="E148" t="s">
         <v>189</v>
       </c>
       <c r="F148" s="4" t="s">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="G148" s="4" t="s">
-        <v>239</v>
+        <v>259</v>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="B149" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="C149" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="D149" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="E149" t="s">
         <v>189</v>
       </c>
       <c r="F149" s="4" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>243</v>
+        <v>262</v>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="s">
-        <v>244</v>
+        <v>263</v>
       </c>
       <c r="B150" t="s">
-        <v>244</v>
+        <v>263</v>
       </c>
       <c r="C150" t="s">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="D150" t="s">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="E150" t="s">
         <v>189</v>
       </c>
       <c r="F150" s="4" t="s">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="G150" s="4" t="s">
-        <v>247</v>
+        <v>265</v>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="B151" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="C151" t="s">
-        <v>249</v>
+        <v>646</v>
       </c>
       <c r="D151" t="s">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="E151" t="s">
         <v>189</v>
       </c>
       <c r="F151" s="4" t="s">
-        <v>250</v>
+        <v>647</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>251</v>
+        <v>647</v>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="B152" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="C152" t="s">
-        <v>253</v>
+        <v>648</v>
       </c>
       <c r="D152" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="E152" t="s">
         <v>189</v>
       </c>
       <c r="F152" s="4" t="s">
-        <v>254</v>
+        <v>649</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>255</v>
+        <v>650</v>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="B153" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="C153" t="s">
-        <v>257</v>
+        <v>651</v>
       </c>
       <c r="D153" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="E153" t="s">
         <v>189</v>
       </c>
       <c r="F153" s="4" t="s">
-        <v>258</v>
+        <v>652</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>259</v>
+        <v>653</v>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B154" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="C154" t="s">
-        <v>261</v>
+        <v>654</v>
       </c>
       <c r="D154" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="E154" t="s">
         <v>189</v>
       </c>
       <c r="F154" s="4" t="s">
-        <v>262</v>
+        <v>655</v>
       </c>
       <c r="G154" s="4" t="s">
-        <v>263</v>
+        <v>656</v>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B155" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C155" t="s">
-        <v>265</v>
+        <v>657</v>
       </c>
       <c r="D155" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E155" t="s">
         <v>189</v>
       </c>
       <c r="F155" s="4" t="s">
-        <v>266</v>
+        <v>658</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>266</v>
+        <v>659</v>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="s">
+        <v>266</v>
+      </c>
+      <c r="B156" t="s">
+        <v>266</v>
+      </c>
+      <c r="C156" t="s">
+        <v>660</v>
+      </c>
+      <c r="D156" t="s">
         <v>267</v>
       </c>
-      <c r="B156" t="s">
-        <v>267</v>
-      </c>
-      <c r="C156" t="s">
-        <v>268</v>
-      </c>
-      <c r="D156" t="s">
-        <v>268</v>
-      </c>
       <c r="E156" t="s">
         <v>189</v>
       </c>
       <c r="F156" s="4" t="s">
-        <v>269</v>
+        <v>661</v>
       </c>
       <c r="G156" s="4" t="s">
-        <v>269</v>
+        <v>662</v>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B157" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C157" t="s">
-        <v>642</v>
+        <v>663</v>
       </c>
       <c r="D157" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E157" t="s">
         <v>189</v>
       </c>
       <c r="F157" s="4" t="s">
-        <v>643</v>
+        <v>664</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>643</v>
+        <v>665</v>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B158" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C158" t="s">
-        <v>644</v>
+        <v>666</v>
       </c>
       <c r="D158" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E158" t="s">
         <v>189</v>
       </c>
       <c r="F158" s="4" t="s">
-        <v>645</v>
+        <v>667</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>646</v>
+        <v>667</v>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B159" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C159" t="s">
-        <v>647</v>
+        <v>668</v>
       </c>
       <c r="D159" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E159" t="s">
         <v>189</v>
       </c>
       <c r="F159" s="4" t="s">
-        <v>648</v>
+        <v>669</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>649</v>
+        <v>670</v>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B160" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C160" t="s">
-        <v>650</v>
+        <v>671</v>
       </c>
       <c r="D160" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E160" t="s">
         <v>189</v>
       </c>
       <c r="F160" s="4" t="s">
-        <v>651</v>
+        <v>672</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>652</v>
+        <v>673</v>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B161" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C161" t="s">
-        <v>653</v>
+        <v>674</v>
       </c>
       <c r="D161" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E161" t="s">
         <v>189</v>
       </c>
       <c r="F161" s="4" t="s">
-        <v>654</v>
+        <v>675</v>
       </c>
       <c r="G161" s="4" t="s">
-        <v>655</v>
+        <v>676</v>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B162" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C162" t="s">
-        <v>656</v>
+        <v>677</v>
       </c>
       <c r="D162" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E162" t="s">
         <v>189</v>
       </c>
       <c r="F162" s="4" t="s">
-        <v>657</v>
+        <v>678</v>
       </c>
       <c r="G162" s="4" t="s">
-        <v>658</v>
+        <v>679</v>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B163" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C163" t="s">
-        <v>659</v>
+        <v>680</v>
       </c>
       <c r="D163" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E163" t="s">
         <v>189</v>
       </c>
       <c r="F163" s="4" t="s">
-        <v>660</v>
+        <v>681</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>661</v>
+        <v>682</v>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B164" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C164" t="s">
-        <v>662</v>
+        <v>683</v>
       </c>
       <c r="D164" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E164" t="s">
         <v>189</v>
       </c>
       <c r="F164" s="4" t="s">
-        <v>663</v>
+        <v>684</v>
       </c>
       <c r="G164" s="4" t="s">
-        <v>663</v>
+        <v>685</v>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B165" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C165" t="s">
-        <v>664</v>
+        <v>686</v>
       </c>
       <c r="D165" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E165" t="s">
         <v>189</v>
       </c>
       <c r="F165" s="4" t="s">
-        <v>665</v>
+        <v>687</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>666</v>
+        <v>688</v>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B166" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C166" t="s">
-        <v>667</v>
+        <v>689</v>
       </c>
       <c r="D166" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E166" t="s">
         <v>189</v>
       </c>
       <c r="F166" s="4" t="s">
-        <v>668</v>
+        <v>690</v>
       </c>
       <c r="G166" s="4" t="s">
-        <v>669</v>
+        <v>690</v>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B167" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C167" t="s">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="D167" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E167" t="s">
         <v>189</v>
       </c>
       <c r="F167" s="4" t="s">
-        <v>671</v>
+        <v>692</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>672</v>
+        <v>693</v>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B168" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C168" t="s">
-        <v>673</v>
+        <v>694</v>
       </c>
       <c r="D168" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E168" t="s">
         <v>189</v>
       </c>
       <c r="F168" s="4" t="s">
-        <v>674</v>
+        <v>695</v>
       </c>
       <c r="G168" s="4" t="s">
-        <v>675</v>
+        <v>696</v>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B169" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C169" t="s">
-        <v>676</v>
+        <v>697</v>
       </c>
       <c r="D169" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E169" t="s">
         <v>189</v>
       </c>
       <c r="F169" s="4" t="s">
-        <v>677</v>
+        <v>698</v>
       </c>
       <c r="G169" s="4" t="s">
-        <v>678</v>
+        <v>698</v>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B170" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C170" t="s">
-        <v>679</v>
+        <v>699</v>
       </c>
       <c r="D170" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E170" t="s">
         <v>189</v>
       </c>
       <c r="F170" s="4" t="s">
-        <v>680</v>
+        <v>700</v>
       </c>
       <c r="G170" s="4" t="s">
-        <v>681</v>
+        <v>700</v>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B171" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C171" t="s">
-        <v>682</v>
+        <v>701</v>
       </c>
       <c r="D171" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E171" t="s">
         <v>189</v>
       </c>
       <c r="F171" s="4" t="s">
-        <v>683</v>
+        <v>702</v>
       </c>
       <c r="G171" s="4" t="s">
-        <v>684</v>
+        <v>703</v>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B172" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C172" t="s">
-        <v>685</v>
+        <v>704</v>
       </c>
       <c r="D172" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E172" t="s">
         <v>189</v>
       </c>
       <c r="F172" s="4" t="s">
-        <v>686</v>
+        <v>705</v>
       </c>
       <c r="G172" s="4" t="s">
-        <v>686</v>
+        <v>706</v>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
@@ -8131,364 +8231,364 @@
         <v>270</v>
       </c>
       <c r="C173" t="s">
-        <v>687</v>
+        <v>271</v>
       </c>
       <c r="D173" t="s">
         <v>271</v>
       </c>
       <c r="E173" t="s">
-        <v>189</v>
+        <v>274</v>
       </c>
       <c r="F173" s="4" t="s">
-        <v>688</v>
+        <v>272</v>
       </c>
       <c r="G173" s="4" t="s">
-        <v>689</v>
+        <v>273</v>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="B174" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C174" t="s">
-        <v>690</v>
+        <v>276</v>
       </c>
       <c r="D174" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="E174" t="s">
-        <v>189</v>
+        <v>274</v>
       </c>
       <c r="F174" s="4" t="s">
-        <v>691</v>
+        <v>707</v>
       </c>
       <c r="G174" s="4" t="s">
-        <v>692</v>
+        <v>708</v>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="B175" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C175" t="s">
-        <v>693</v>
+        <v>709</v>
       </c>
       <c r="D175" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="E175" t="s">
-        <v>189</v>
+        <v>274</v>
       </c>
       <c r="F175" s="4" t="s">
-        <v>694</v>
+        <v>710</v>
       </c>
       <c r="G175" s="4" t="s">
-        <v>694</v>
+        <v>710</v>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="B176" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C176" t="s">
-        <v>695</v>
+        <v>711</v>
       </c>
       <c r="D176" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="E176" t="s">
-        <v>189</v>
+        <v>274</v>
       </c>
       <c r="F176" s="4" t="s">
-        <v>696</v>
+        <v>712</v>
       </c>
       <c r="G176" s="4" t="s">
-        <v>696</v>
+        <v>712</v>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="B177" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C177" t="s">
-        <v>697</v>
+        <v>713</v>
       </c>
       <c r="D177" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="E177" t="s">
-        <v>189</v>
+        <v>274</v>
       </c>
       <c r="F177" s="4" t="s">
-        <v>698</v>
+        <v>714</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>699</v>
+        <v>714</v>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="B178" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C178" t="s">
-        <v>700</v>
+        <v>715</v>
       </c>
       <c r="D178" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="E178" t="s">
-        <v>189</v>
+        <v>274</v>
       </c>
       <c r="F178" s="4" t="s">
-        <v>701</v>
+        <v>716</v>
       </c>
       <c r="G178" s="4" t="s">
-        <v>702</v>
+        <v>716</v>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="s">
+        <v>275</v>
+      </c>
+      <c r="B179" t="s">
+        <v>275</v>
+      </c>
+      <c r="C179" t="s">
+        <v>717</v>
+      </c>
+      <c r="D179" t="s">
+        <v>276</v>
+      </c>
+      <c r="E179" t="s">
         <v>274</v>
       </c>
-      <c r="B179" t="s">
-        <v>274</v>
-      </c>
-      <c r="C179" t="s">
-        <v>275</v>
-      </c>
-      <c r="D179" t="s">
-        <v>275</v>
-      </c>
-      <c r="E179" t="s">
-        <v>278</v>
-      </c>
       <c r="F179" s="4" t="s">
-        <v>276</v>
+        <v>718</v>
       </c>
       <c r="G179" s="4" t="s">
-        <v>277</v>
+        <v>719</v>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="s">
-        <v>279</v>
+        <v>720</v>
       </c>
       <c r="B180" t="s">
         <v>279</v>
       </c>
       <c r="C180" t="s">
-        <v>280</v>
+        <v>721</v>
       </c>
       <c r="D180" t="s">
         <v>280</v>
       </c>
       <c r="E180" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F180" s="4" t="s">
-        <v>703</v>
+        <v>722</v>
       </c>
       <c r="G180" s="4" t="s">
-        <v>704</v>
+        <v>723</v>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="s">
-        <v>279</v>
+        <v>724</v>
       </c>
       <c r="B181" t="s">
         <v>279</v>
       </c>
       <c r="C181" t="s">
-        <v>705</v>
+        <v>725</v>
       </c>
       <c r="D181" t="s">
         <v>280</v>
       </c>
       <c r="E181" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F181" s="4" t="s">
-        <v>706</v>
+        <v>726</v>
       </c>
       <c r="G181" s="4" t="s">
-        <v>706</v>
+        <v>727</v>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B182" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C182" t="s">
-        <v>707</v>
+        <v>284</v>
       </c>
       <c r="D182" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="E182" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F182" s="4" t="s">
-        <v>708</v>
+        <v>285</v>
       </c>
       <c r="G182" s="4" t="s">
-        <v>708</v>
+        <v>286</v>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="B183" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="C183" t="s">
-        <v>709</v>
+        <v>288</v>
       </c>
       <c r="D183" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="E183" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F183" s="4" t="s">
-        <v>710</v>
+        <v>289</v>
       </c>
       <c r="G183" s="4" t="s">
-        <v>710</v>
+        <v>290</v>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="B184" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="C184" t="s">
-        <v>711</v>
+        <v>728</v>
       </c>
       <c r="D184" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="E184" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F184" s="4" t="s">
-        <v>712</v>
+        <v>729</v>
       </c>
       <c r="G184" s="4" t="s">
-        <v>712</v>
+        <v>730</v>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="B185" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="C185" t="s">
-        <v>713</v>
+        <v>731</v>
       </c>
       <c r="D185" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="E185" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F185" s="4" t="s">
-        <v>714</v>
+        <v>732</v>
       </c>
       <c r="G185" s="4" t="s">
-        <v>715</v>
+        <v>733</v>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="s">
-        <v>716</v>
+        <v>291</v>
       </c>
       <c r="B186" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="C186" t="s">
-        <v>717</v>
+        <v>734</v>
       </c>
       <c r="D186" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="E186" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F186" s="4" t="s">
-        <v>718</v>
+        <v>735</v>
       </c>
       <c r="G186" s="4" t="s">
-        <v>719</v>
+        <v>736</v>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="s">
-        <v>720</v>
+        <v>291</v>
       </c>
       <c r="B187" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="C187" t="s">
-        <v>721</v>
+        <v>737</v>
       </c>
       <c r="D187" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="E187" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F187" s="4" t="s">
-        <v>722</v>
+        <v>738</v>
       </c>
       <c r="G187" s="4" t="s">
-        <v>723</v>
+        <v>739</v>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B188" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C188" t="s">
-        <v>288</v>
+        <v>740</v>
       </c>
       <c r="D188" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E188" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F188" s="4" t="s">
-        <v>289</v>
+        <v>741</v>
       </c>
       <c r="G188" s="4" t="s">
-        <v>290</v>
+        <v>742</v>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
@@ -8505,13 +8605,13 @@
         <v>292</v>
       </c>
       <c r="E189" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F189" s="4" t="s">
-        <v>293</v>
+        <v>743</v>
       </c>
       <c r="G189" s="4" t="s">
-        <v>294</v>
+        <v>744</v>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
@@ -8522,433 +8622,433 @@
         <v>295</v>
       </c>
       <c r="C190" t="s">
-        <v>724</v>
+        <v>296</v>
       </c>
       <c r="D190" t="s">
         <v>296</v>
       </c>
       <c r="E190" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F190" s="4" t="s">
-        <v>725</v>
+        <v>297</v>
       </c>
       <c r="G190" s="4" t="s">
-        <v>726</v>
+        <v>298</v>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="s">
-        <v>295</v>
+        <v>745</v>
       </c>
       <c r="B191" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C191" t="s">
-        <v>727</v>
+        <v>746</v>
       </c>
       <c r="D191" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E191" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F191" s="4" t="s">
-        <v>728</v>
+        <v>747</v>
       </c>
       <c r="G191" s="4" t="s">
-        <v>729</v>
+        <v>748</v>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="s">
-        <v>295</v>
+        <v>749</v>
       </c>
       <c r="B192" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C192" t="s">
-        <v>730</v>
+        <v>750</v>
       </c>
       <c r="D192" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E192" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F192" s="4" t="s">
-        <v>731</v>
+        <v>751</v>
       </c>
       <c r="G192" s="4" t="s">
-        <v>732</v>
+        <v>752</v>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="s">
-        <v>295</v>
+        <v>753</v>
       </c>
       <c r="B193" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C193" t="s">
-        <v>733</v>
+        <v>754</v>
       </c>
       <c r="D193" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E193" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F193" s="4" t="s">
-        <v>734</v>
+        <v>755</v>
       </c>
       <c r="G193" s="4" t="s">
-        <v>735</v>
+        <v>756</v>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="B194" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="C194" t="s">
-        <v>736</v>
+        <v>757</v>
       </c>
       <c r="D194" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="E194" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F194" s="4" t="s">
-        <v>737</v>
+        <v>758</v>
       </c>
       <c r="G194" s="4" t="s">
-        <v>738</v>
+        <v>758</v>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="B195" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="C195" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="D195" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="E195" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F195" s="4" t="s">
-        <v>739</v>
+        <v>759</v>
       </c>
       <c r="G195" s="4" t="s">
-        <v>740</v>
+        <v>760</v>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="B196" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="C196" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="D196" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="E196" t="s">
-        <v>278</v>
+        <v>311</v>
       </c>
       <c r="F196" s="4" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="G196" s="4" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="s">
-        <v>741</v>
+        <v>312</v>
       </c>
       <c r="B197" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="C197" t="s">
-        <v>742</v>
+        <v>313</v>
       </c>
       <c r="D197" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="E197" t="s">
-        <v>278</v>
+        <v>311</v>
       </c>
       <c r="F197" s="4" t="s">
-        <v>743</v>
+        <v>314</v>
       </c>
       <c r="G197" s="4" t="s">
-        <v>744</v>
+        <v>315</v>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="s">
-        <v>745</v>
+        <v>316</v>
       </c>
       <c r="B198" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="C198" t="s">
-        <v>746</v>
+        <v>317</v>
       </c>
       <c r="D198" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="E198" t="s">
-        <v>278</v>
+        <v>311</v>
       </c>
       <c r="F198" s="4" t="s">
-        <v>747</v>
+        <v>318</v>
       </c>
       <c r="G198" s="4" t="s">
-        <v>748</v>
+        <v>318</v>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="s">
-        <v>749</v>
+        <v>319</v>
       </c>
       <c r="B199" t="s">
-        <v>303</v>
+        <v>319</v>
       </c>
       <c r="C199" t="s">
-        <v>750</v>
+        <v>320</v>
       </c>
       <c r="D199" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="E199" t="s">
-        <v>278</v>
+        <v>311</v>
       </c>
       <c r="F199" s="4" t="s">
-        <v>751</v>
+        <v>321</v>
       </c>
       <c r="G199" s="4" t="s">
-        <v>752</v>
+        <v>322</v>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="s">
-        <v>307</v>
+        <v>323</v>
       </c>
       <c r="B200" t="s">
-        <v>307</v>
+        <v>323</v>
       </c>
       <c r="C200" t="s">
-        <v>753</v>
+        <v>324</v>
       </c>
       <c r="D200" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="E200" t="s">
-        <v>278</v>
+        <v>311</v>
       </c>
       <c r="F200" s="4" t="s">
-        <v>754</v>
+        <v>325</v>
       </c>
       <c r="G200" s="4" t="s">
-        <v>754</v>
+        <v>326</v>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="s">
-        <v>307</v>
+        <v>327</v>
       </c>
       <c r="B201" t="s">
-        <v>307</v>
+        <v>327</v>
       </c>
       <c r="C201" t="s">
-        <v>308</v>
+        <v>328</v>
       </c>
       <c r="D201" t="s">
-        <v>308</v>
+        <v>328</v>
       </c>
       <c r="E201" t="s">
-        <v>278</v>
+        <v>311</v>
       </c>
       <c r="F201" s="4" t="s">
-        <v>755</v>
+        <v>329</v>
       </c>
       <c r="G201" s="4" t="s">
-        <v>756</v>
+        <v>330</v>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="s">
+        <v>331</v>
+      </c>
+      <c r="B202" t="s">
+        <v>331</v>
+      </c>
+      <c r="C202" t="s">
+        <v>761</v>
+      </c>
+      <c r="D202" t="s">
+        <v>332</v>
+      </c>
+      <c r="E202" t="s">
         <v>311</v>
       </c>
-      <c r="B202" t="s">
-        <v>311</v>
-      </c>
-      <c r="C202" t="s">
-        <v>757</v>
-      </c>
-      <c r="D202" t="s">
-        <v>312</v>
-      </c>
-      <c r="E202" t="s">
-        <v>315</v>
-      </c>
       <c r="F202" s="4" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="G202" s="4" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="s">
+        <v>331</v>
+      </c>
+      <c r="B203" t="s">
+        <v>331</v>
+      </c>
+      <c r="C203" t="s">
+        <v>764</v>
+      </c>
+      <c r="D203" t="s">
+        <v>332</v>
+      </c>
+      <c r="E203" t="s">
         <v>311</v>
       </c>
-      <c r="B203" t="s">
-        <v>311</v>
-      </c>
-      <c r="C203" t="s">
-        <v>760</v>
-      </c>
-      <c r="D203" t="s">
-        <v>312</v>
-      </c>
-      <c r="E203" t="s">
-        <v>315</v>
-      </c>
       <c r="F203" s="4" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="G203" s="4" t="s">
-        <v>761</v>
+        <v>766</v>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="s">
+        <v>331</v>
+      </c>
+      <c r="B204" t="s">
+        <v>331</v>
+      </c>
+      <c r="C204" t="s">
+        <v>767</v>
+      </c>
+      <c r="D204" t="s">
+        <v>332</v>
+      </c>
+      <c r="E204" t="s">
         <v>311</v>
       </c>
-      <c r="B204" t="s">
-        <v>311</v>
-      </c>
-      <c r="C204" t="s">
-        <v>762</v>
-      </c>
-      <c r="D204" t="s">
-        <v>312</v>
-      </c>
-      <c r="E204" t="s">
-        <v>315</v>
-      </c>
       <c r="F204" s="4" t="s">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="G204" s="4" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="s">
+        <v>331</v>
+      </c>
+      <c r="B205" t="s">
+        <v>331</v>
+      </c>
+      <c r="C205" t="s">
+        <v>769</v>
+      </c>
+      <c r="D205" t="s">
+        <v>332</v>
+      </c>
+      <c r="E205" t="s">
         <v>311</v>
       </c>
-      <c r="B205" t="s">
-        <v>311</v>
-      </c>
-      <c r="C205" t="s">
-        <v>765</v>
-      </c>
-      <c r="D205" t="s">
-        <v>312</v>
-      </c>
-      <c r="E205" t="s">
-        <v>315</v>
-      </c>
       <c r="F205" s="4" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="G205" s="4" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="s">
+        <v>331</v>
+      </c>
+      <c r="B206" t="s">
+        <v>331</v>
+      </c>
+      <c r="C206" t="s">
+        <v>772</v>
+      </c>
+      <c r="D206" t="s">
+        <v>332</v>
+      </c>
+      <c r="E206" t="s">
         <v>311</v>
       </c>
-      <c r="B206" t="s">
-        <v>311</v>
-      </c>
-      <c r="C206" t="s">
-        <v>768</v>
-      </c>
-      <c r="D206" t="s">
-        <v>312</v>
-      </c>
-      <c r="E206" t="s">
-        <v>315</v>
-      </c>
       <c r="F206" s="4" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="G206" s="4" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="s">
+        <v>331</v>
+      </c>
+      <c r="B207" t="s">
+        <v>331</v>
+      </c>
+      <c r="C207" t="s">
+        <v>775</v>
+      </c>
+      <c r="D207" t="s">
+        <v>332</v>
+      </c>
+      <c r="E207" t="s">
         <v>311</v>
       </c>
-      <c r="B207" t="s">
-        <v>311</v>
-      </c>
-      <c r="C207" t="s">
-        <v>771</v>
-      </c>
-      <c r="D207" t="s">
-        <v>312</v>
-      </c>
-      <c r="E207" t="s">
-        <v>315</v>
-      </c>
       <c r="F207" s="4" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="G207" s="4" t="s">
-        <v>772</v>
+        <v>777</v>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="s">
-        <v>316</v>
+        <v>335</v>
       </c>
       <c r="B208" t="s">
-        <v>316</v>
+        <v>335</v>
       </c>
       <c r="C208" t="s">
-        <v>317</v>
+        <v>336</v>
       </c>
       <c r="D208" t="s">
-        <v>317</v>
+        <v>336</v>
       </c>
       <c r="E208" t="s">
-        <v>320</v>
+        <v>339</v>
       </c>
       <c r="F208" s="4" t="s">
-        <v>318</v>
+        <v>337</v>
       </c>
       <c r="G208" s="4" t="s">
-        <v>319</v>
+        <v>338</v>
       </c>
     </row>
   </sheetData>
